--- a/app/src/main/assets/methodmesh/odk_templates/nfc/example_odk_showcase_nfc_credential_provisioning.xlsx
+++ b/app/src/main/assets/methodmesh/odk_templates/nfc/example_odk_showcase_nfc_credential_provisioning.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R297f5b6f5a2c47b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R59f96ddbab594d22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R97e7cb7a07d649f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R1146ba0ac5ab4905"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R10f961d3b91746d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R7ec4782b62e4454e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,6 +23,7 @@
     <x:font>
       <x:b/>
       <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -35,7 +36,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFE2E8F0"/>
+        <x:fgColor rgb="FF0F766E"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -46,7 +47,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="9">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -60,9 +61,6 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -267,19 +265,18 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="20" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="36" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="40" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="11" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="32" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="38" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="42" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="120" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -296,46 +293,39 @@
         <x:v>hint</x:v>
       </x:c>
       <x:c r="E1" s="4" t="str">
+        <x:v>required</x:v>
+      </x:c>
+      <x:c r="F1" s="4" t="str">
+        <x:v>relevant</x:v>
+      </x:c>
+      <x:c r="G1" s="4" t="str">
+        <x:v>constraint</x:v>
+      </x:c>
+      <x:c r="H1" s="4" t="str">
+        <x:v>constraint_message</x:v>
+      </x:c>
+      <x:c r="I1" s="4" t="str">
+        <x:v>calculation</x:v>
+      </x:c>
+      <x:c r="J1" s="4" t="str">
         <x:v>appearance</x:v>
-      </x:c>
-      <x:c r="F1" s="4" t="str">
-        <x:v>required</x:v>
-      </x:c>
-      <x:c r="G1" s="4" t="str">
-        <x:v>relevant</x:v>
-      </x:c>
-      <x:c r="H1" s="4" t="str">
-        <x:v>constraint</x:v>
-      </x:c>
-      <x:c r="I1" s="4" t="str">
-        <x:v>constraint_message</x:v>
-      </x:c>
-      <x:c r="J1" s="4" t="str">
-        <x:v>calculation</x:v>
       </x:c>
       <x:c r="K1" s="4" t="str">
         <x:v>default</x:v>
       </x:c>
       <x:c r="L1" s="4" t="str">
-        <x:v>read_only</x:v>
-      </x:c>
-      <x:c r="M1" s="4" t="str">
         <x:v>body::intent</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="8" t="str">
-        <x:v>note</x:v>
+        <x:v>start</x:v>
       </x:c>
       <x:c r="B2" s="8" t="str">
-        <x:v>intro</x:v>
-      </x:c>
-      <x:c r="C2" s="8" t="str">
-        <x:v>MethodMesh NFC — nfc_credential_provisioning</x:v>
-      </x:c>
-      <x:c r="D2" s="8" t="str">
-        <x:v>Create a PIN-protected portable NFC credential</x:v>
-      </x:c>
+        <x:v>start</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="str"/>
+      <x:c r="D2" s="8" t="str"/>
       <x:c r="E2" s="8" t="str"/>
       <x:c r="F2" s="8" t="str"/>
       <x:c r="G2" s="8" t="str"/>
@@ -344,24 +334,17 @@
       <x:c r="J2" s="8" t="str"/>
       <x:c r="K2" s="8" t="str"/>
       <x:c r="L2" s="8" t="str"/>
-      <x:c r="M2" s="8" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="8" t="str">
-        <x:v>begin_group</x:v>
+        <x:v>end</x:v>
       </x:c>
       <x:c r="B3" s="8" t="str">
-        <x:v>run_nfc_credential_provisioning</x:v>
-      </x:c>
-      <x:c r="C3" s="8" t="str">
-        <x:v>Run nfc_credential_provisioning</x:v>
-      </x:c>
-      <x:c r="D3" s="8" t="str">
-        <x:v>This form invokes only this MethodMesh capability. Inputs shown here are only those relevant to this call; capability interaction may continue in the native MethodMesh surface and return on Commit.</x:v>
-      </x:c>
-      <x:c r="E3" s="8" t="str">
-        <x:v>field-list</x:v>
-      </x:c>
+        <x:v>end</x:v>
+      </x:c>
+      <x:c r="C3" s="8" t="str"/>
+      <x:c r="D3" s="8" t="str"/>
+      <x:c r="E3" s="8" t="str"/>
       <x:c r="F3" s="8" t="str"/>
       <x:c r="G3" s="8" t="str"/>
       <x:c r="H3" s="8" t="str"/>
@@ -369,22 +352,19 @@
       <x:c r="J3" s="8" t="str"/>
       <x:c r="K3" s="8" t="str"/>
       <x:c r="L3" s="8" t="str"/>
-      <x:c r="M3" s="8" t="str">
-        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='nfc_credential_provisioning',input_payload_mode='FULL',return_mode='flat')</x:v>
-      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="8" t="str">
         <x:v>note</x:v>
       </x:c>
       <x:c r="B4" s="8" t="str">
-        <x:v>native_interaction</x:v>
+        <x:v>introduction</x:v>
       </x:c>
       <x:c r="C4" s="8" t="str">
-        <x:v>Complete the capability in MethodMesh, then Commit to return.</x:v>
+        <x:v>Provision a MethodMesh NFC credential</x:v>
       </x:c>
       <x:c r="D4" s="8" t="str">
-        <x:v>No undocumented ODK inputs have been invented for this showcase.</x:v>
+        <x:v>Study identity and governance remain in ODK. MethodMesh writes only the portable cryptographic credential and returns the issuer identity and audit evidence.</x:v>
       </x:c>
       <x:c r="E4" s="8" t="str"/>
       <x:c r="F4" s="8" t="str"/>
@@ -394,77 +374,70 @@
       <x:c r="J4" s="8" t="str"/>
       <x:c r="K4" s="8" t="str"/>
       <x:c r="L4" s="8" t="str"/>
-      <x:c r="M4" s="8" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>begin group</x:v>
       </x:c>
       <x:c r="B5" s="8" t="str">
-        <x:v>methodmesh_status</x:v>
+        <x:v>study_context</x:v>
       </x:c>
       <x:c r="C5" s="8" t="str">
-        <x:v>Methodmesh Status</x:v>
-      </x:c>
-      <x:c r="D5" s="8" t="str">
-        <x:v>Shared MethodMesh transport status, where projected by the runtime.</x:v>
-      </x:c>
-      <x:c r="E5" s="8" t="str">
-        <x:v>hidden-answer</x:v>
-      </x:c>
+        <x:v>Credential holder and study context</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="str"/>
+      <x:c r="E5" s="8" t="str"/>
       <x:c r="F5" s="8" t="str"/>
       <x:c r="G5" s="8" t="str"/>
       <x:c r="H5" s="8" t="str"/>
       <x:c r="I5" s="8" t="str"/>
-      <x:c r="J5" s="8" t="str"/>
+      <x:c r="J5" s="8" t="str">
+        <x:v>field-list</x:v>
+      </x:c>
       <x:c r="K5" s="8" t="str"/>
-      <x:c r="L5" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="M5" s="8" t="str"/>
+      <x:c r="L5" s="8" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B6" s="8" t="str">
-        <x:v>provision_success</x:v>
+        <x:v>study_id</x:v>
       </x:c>
       <x:c r="C6" s="8" t="str">
-        <x:v>Provision Success</x:v>
+        <x:v>Study / protocol ID</x:v>
       </x:c>
       <x:c r="D6" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
+        <x:v>Stable study or protocol code.</x:v>
       </x:c>
       <x:c r="E6" s="8" t="str">
-        <x:v>hidden-answer</x:v>
+        <x:v>yes</x:v>
       </x:c>
       <x:c r="F6" s="8" t="str"/>
-      <x:c r="G6" s="8" t="str"/>
-      <x:c r="H6" s="8" t="str"/>
+      <x:c r="G6" s="8" t="str">
+        <x:v>string-length(.) &lt;= 64</x:v>
+      </x:c>
+      <x:c r="H6" s="8" t="str">
+        <x:v>Use a study ID of 64 characters or fewer.</x:v>
+      </x:c>
       <x:c r="I6" s="8" t="str"/>
       <x:c r="J6" s="8" t="str"/>
       <x:c r="K6" s="8" t="str"/>
-      <x:c r="L6" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="M6" s="8" t="str"/>
+      <x:c r="L6" s="8" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>select_one holder_type</x:v>
       </x:c>
       <x:c r="B7" s="8" t="str">
-        <x:v>provision_message</x:v>
+        <x:v>holder_type</x:v>
       </x:c>
       <x:c r="C7" s="8" t="str">
-        <x:v>Provision Message</x:v>
-      </x:c>
-      <x:c r="D7" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
-      </x:c>
+        <x:v>Credential holder type</x:v>
+      </x:c>
+      <x:c r="D7" s="8" t="str"/>
       <x:c r="E7" s="8" t="str">
-        <x:v>hidden-answer</x:v>
+        <x:v>yes</x:v>
       </x:c>
       <x:c r="F7" s="8" t="str"/>
       <x:c r="G7" s="8" t="str"/>
@@ -472,53 +445,51 @@
       <x:c r="I7" s="8" t="str"/>
       <x:c r="J7" s="8" t="str"/>
       <x:c r="K7" s="8" t="str"/>
-      <x:c r="L7" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="M7" s="8" t="str"/>
+      <x:c r="L7" s="8" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B8" s="8" t="str">
-        <x:v>credential_id</x:v>
+        <x:v>credential_subject_id_input</x:v>
       </x:c>
       <x:c r="C8" s="8" t="str">
-        <x:v>Credential Id</x:v>
+        <x:v>Credential subject / registry ID</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
+        <x:v>Use a stable pseudonymous ID, not a name or email. This is the identifier passed into the portable credential.</x:v>
       </x:c>
       <x:c r="E8" s="8" t="str">
-        <x:v>hidden-answer</x:v>
+        <x:v>yes</x:v>
       </x:c>
       <x:c r="F8" s="8" t="str"/>
-      <x:c r="G8" s="8" t="str"/>
-      <x:c r="H8" s="8" t="str"/>
+      <x:c r="G8" s="8" t="str">
+        <x:v>string-length(.) &gt;= 2 and string-length(.) &lt;= 64</x:v>
+      </x:c>
+      <x:c r="H8" s="8" t="str">
+        <x:v>Use a stable ID between 2 and 64 characters.</x:v>
+      </x:c>
       <x:c r="I8" s="8" t="str"/>
       <x:c r="J8" s="8" t="str"/>
       <x:c r="K8" s="8" t="str"/>
-      <x:c r="L8" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="M8" s="8" t="str"/>
+      <x:c r="L8" s="8" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B9" s="8" t="str">
-        <x:v>credential_issued_time_iso</x:v>
+        <x:v>holder_display_name</x:v>
       </x:c>
       <x:c r="C9" s="8" t="str">
-        <x:v>Credential Issued Time Iso</x:v>
+        <x:v>Name / display name</x:v>
       </x:c>
       <x:c r="D9" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
+        <x:v>Registry field only; not written to the NFC credential.</x:v>
       </x:c>
       <x:c r="E9" s="8" t="str">
-        <x:v>hidden-answer</x:v>
+        <x:v>yes</x:v>
       </x:c>
       <x:c r="F9" s="8" t="str"/>
       <x:c r="G9" s="8" t="str"/>
@@ -526,26 +497,21 @@
       <x:c r="I9" s="8" t="str"/>
       <x:c r="J9" s="8" t="str"/>
       <x:c r="K9" s="8" t="str"/>
-      <x:c r="L9" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="M9" s="8" t="str"/>
+      <x:c r="L9" s="8" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>select_one credential_role</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
-        <x:v>credential_subject</x:v>
+        <x:v>holder_role</x:v>
       </x:c>
       <x:c r="C10" s="8" t="str">
-        <x:v>Credential Subject</x:v>
-      </x:c>
-      <x:c r="D10" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
-      </x:c>
+        <x:v>Study role</x:v>
+      </x:c>
+      <x:c r="D10" s="8" t="str"/>
       <x:c r="E10" s="8" t="str">
-        <x:v>hidden-answer</x:v>
+        <x:v>yes</x:v>
       </x:c>
       <x:c r="F10" s="8" t="str"/>
       <x:c r="G10" s="8" t="str"/>
@@ -553,53 +519,47 @@
       <x:c r="I10" s="8" t="str"/>
       <x:c r="J10" s="8" t="str"/>
       <x:c r="K10" s="8" t="str"/>
-      <x:c r="L10" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="M10" s="8" t="str"/>
+      <x:c r="L10" s="8" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B11" s="8" t="str">
-        <x:v>credential_payload_json</x:v>
+        <x:v>holder_role_other</x:v>
       </x:c>
       <x:c r="C11" s="8" t="str">
-        <x:v>Credential Payload Json</x:v>
-      </x:c>
-      <x:c r="D11" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
-      </x:c>
+        <x:v>Other role</x:v>
+      </x:c>
+      <x:c r="D11" s="8" t="str"/>
       <x:c r="E11" s="8" t="str">
-        <x:v>hidden-answer</x:v>
-      </x:c>
-      <x:c r="F11" s="8" t="str"/>
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F11" s="8" t="str">
+        <x:v>${holder_role} = 'other'</x:v>
+      </x:c>
       <x:c r="G11" s="8" t="str"/>
       <x:c r="H11" s="8" t="str"/>
       <x:c r="I11" s="8" t="str"/>
       <x:c r="J11" s="8" t="str"/>
       <x:c r="K11" s="8" t="str"/>
-      <x:c r="L11" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="M11" s="8" t="str"/>
+      <x:c r="L11" s="8" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B12" s="8" t="str">
-        <x:v>credential_provisioning_json</x:v>
+        <x:v>site_code</x:v>
       </x:c>
       <x:c r="C12" s="8" t="str">
-        <x:v>Credential Provisioning Json</x:v>
+        <x:v>Site / location code</x:v>
       </x:c>
       <x:c r="D12" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
+        <x:v>Study site, clinic, laboratory or operating location.</x:v>
       </x:c>
       <x:c r="E12" s="8" t="str">
-        <x:v>hidden-answer</x:v>
+        <x:v>yes</x:v>
       </x:c>
       <x:c r="F12" s="8" t="str"/>
       <x:c r="G12" s="8" t="str"/>
@@ -607,53 +567,45 @@
       <x:c r="I12" s="8" t="str"/>
       <x:c r="J12" s="8" t="str"/>
       <x:c r="K12" s="8" t="str"/>
-      <x:c r="L12" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="M12" s="8" t="str"/>
+      <x:c r="L12" s="8" t="str"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B13" s="8" t="str">
-        <x:v>provisioned_time_iso</x:v>
+        <x:v>organisation</x:v>
       </x:c>
       <x:c r="C13" s="8" t="str">
-        <x:v>Provisioned Time Iso</x:v>
+        <x:v>Organisation / team</x:v>
       </x:c>
       <x:c r="D13" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
-      </x:c>
-      <x:c r="E13" s="8" t="str">
-        <x:v>hidden-answer</x:v>
-      </x:c>
+        <x:v>Optional employing organisation or study team.</x:v>
+      </x:c>
+      <x:c r="E13" s="8" t="str"/>
       <x:c r="F13" s="8" t="str"/>
       <x:c r="G13" s="8" t="str"/>
       <x:c r="H13" s="8" t="str"/>
       <x:c r="I13" s="8" t="str"/>
       <x:c r="J13" s="8" t="str"/>
       <x:c r="K13" s="8" t="str"/>
-      <x:c r="L13" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="M13" s="8" t="str"/>
+      <x:c r="L13" s="8" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>date</x:v>
       </x:c>
       <x:c r="B14" s="8" t="str">
-        <x:v>methodmesh_full_json</x:v>
+        <x:v>valid_from_date</x:v>
       </x:c>
       <x:c r="C14" s="8" t="str">
-        <x:v>Methodmesh Full Json</x:v>
+        <x:v>Credential valid from</x:v>
       </x:c>
       <x:c r="D14" s="8" t="str">
-        <x:v>Shared MethodMesh FULL execution envelope. Retained for complete execution/audit capture; capability-specific return fields are projected separately.</x:v>
+        <x:v>Administrative validity retained by the study registry; not encoded into ROSC1.</x:v>
       </x:c>
       <x:c r="E14" s="8" t="str">
-        <x:v>hidden-answer</x:v>
+        <x:v>yes</x:v>
       </x:c>
       <x:c r="F14" s="8" t="str"/>
       <x:c r="G14" s="8" t="str"/>
@@ -661,42 +613,52 @@
       <x:c r="I14" s="8" t="str"/>
       <x:c r="J14" s="8" t="str"/>
       <x:c r="K14" s="8" t="str"/>
-      <x:c r="L14" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="M14" s="8" t="str"/>
+      <x:c r="L14" s="8" t="str"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="8" t="str">
-        <x:v>end_group</x:v>
-      </x:c>
-      <x:c r="B15" s="8" t="str"/>
-      <x:c r="C15" s="8" t="str"/>
-      <x:c r="D15" s="8" t="str"/>
-      <x:c r="E15" s="8" t="str"/>
+        <x:v>date</x:v>
+      </x:c>
+      <x:c r="B15" s="8" t="str">
+        <x:v>valid_until_date</x:v>
+      </x:c>
+      <x:c r="C15" s="8" t="str">
+        <x:v>Credential valid until</x:v>
+      </x:c>
+      <x:c r="D15" s="8" t="str">
+        <x:v>Administrative validity retained by the study registry; not encoded into ROSC1.</x:v>
+      </x:c>
+      <x:c r="E15" s="8" t="str">
+        <x:v>yes</x:v>
+      </x:c>
       <x:c r="F15" s="8" t="str"/>
-      <x:c r="G15" s="8" t="str"/>
-      <x:c r="H15" s="8" t="str"/>
+      <x:c r="G15" s="8" t="str">
+        <x:v>. &gt;= ${valid_from_date}</x:v>
+      </x:c>
+      <x:c r="H15" s="8" t="str">
+        <x:v>End date must be on or after the start date.</x:v>
+      </x:c>
       <x:c r="I15" s="8" t="str"/>
       <x:c r="J15" s="8" t="str"/>
       <x:c r="K15" s="8" t="str"/>
       <x:c r="L15" s="8" t="str"/>
-      <x:c r="M15" s="8" t="str"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="8" t="str">
-        <x:v>note</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="B16" s="8" t="str">
-        <x:v>return_summary</x:v>
+        <x:v>authorised_by</x:v>
       </x:c>
       <x:c r="C16" s="8" t="str">
-        <x:v>MethodMesh return captured. Status: ${methodmesh_status}</x:v>
+        <x:v>Authorised by</x:v>
       </x:c>
       <x:c r="D16" s="8" t="str">
-        <x:v>Only fields relevant to this capability are stored, plus the shared FULL envelope.</x:v>
-      </x:c>
-      <x:c r="E16" s="8" t="str"/>
+        <x:v>Name or identifier of the person authorising issuance.</x:v>
+      </x:c>
+      <x:c r="E16" s="8" t="str">
+        <x:v>yes</x:v>
+      </x:c>
       <x:c r="F16" s="8" t="str"/>
       <x:c r="G16" s="8" t="str"/>
       <x:c r="H16" s="8" t="str"/>
@@ -704,7 +666,2398 @@
       <x:c r="J16" s="8" t="str"/>
       <x:c r="K16" s="8" t="str"/>
       <x:c r="L16" s="8" t="str"/>
-      <x:c r="M16" s="8" t="str"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="8" t="str">
+        <x:v>select_one provision_reason</x:v>
+      </x:c>
+      <x:c r="B17" s="8" t="str">
+        <x:v>provision_reason</x:v>
+      </x:c>
+      <x:c r="C17" s="8" t="str">
+        <x:v>Reason for issuing credential</x:v>
+      </x:c>
+      <x:c r="D17" s="8" t="str"/>
+      <x:c r="E17" s="8" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F17" s="8" t="str"/>
+      <x:c r="G17" s="8" t="str"/>
+      <x:c r="H17" s="8" t="str"/>
+      <x:c r="I17" s="8" t="str"/>
+      <x:c r="J17" s="8" t="str"/>
+      <x:c r="K17" s="8" t="str"/>
+      <x:c r="L17" s="8" t="str"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B18" s="8" t="str">
+        <x:v>provision_reason_other</x:v>
+      </x:c>
+      <x:c r="C18" s="8" t="str">
+        <x:v>Other issuance reason</x:v>
+      </x:c>
+      <x:c r="D18" s="8" t="str"/>
+      <x:c r="E18" s="8" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F18" s="8" t="str">
+        <x:v>${provision_reason} = 'other'</x:v>
+      </x:c>
+      <x:c r="G18" s="8" t="str"/>
+      <x:c r="H18" s="8" t="str"/>
+      <x:c r="I18" s="8" t="str"/>
+      <x:c r="J18" s="8" t="str"/>
+      <x:c r="K18" s="8" t="str"/>
+      <x:c r="L18" s="8" t="str"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B19" s="8" t="str">
+        <x:v>registry_notes</x:v>
+      </x:c>
+      <x:c r="C19" s="8" t="str">
+        <x:v>Registry notes</x:v>
+      </x:c>
+      <x:c r="D19" s="8" t="str">
+        <x:v>Optional study administration notes. Do not enter the PIN.</x:v>
+      </x:c>
+      <x:c r="E19" s="8" t="str"/>
+      <x:c r="F19" s="8" t="str"/>
+      <x:c r="G19" s="8" t="str"/>
+      <x:c r="H19" s="8" t="str"/>
+      <x:c r="I19" s="8" t="str"/>
+      <x:c r="J19" s="8" t="str">
+        <x:v>multiline</x:v>
+      </x:c>
+      <x:c r="K19" s="8" t="str"/>
+      <x:c r="L19" s="8" t="str"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="8" t="str">
+        <x:v>calculate</x:v>
+      </x:c>
+      <x:c r="B20" s="8" t="str">
+        <x:v>credential_registry_key</x:v>
+      </x:c>
+      <x:c r="C20" s="8" t="str"/>
+      <x:c r="D20" s="8" t="str"/>
+      <x:c r="E20" s="8" t="str"/>
+      <x:c r="F20" s="8" t="str"/>
+      <x:c r="G20" s="8" t="str"/>
+      <x:c r="H20" s="8" t="str"/>
+      <x:c r="I20" s="8" t="str">
+        <x:v>concat(${study_id}, '|', ${credential_subject_id_input})</x:v>
+      </x:c>
+      <x:c r="J20" s="8" t="str"/>
+      <x:c r="K20" s="8" t="str"/>
+      <x:c r="L20" s="8" t="str"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="8" t="str">
+        <x:v>end group</x:v>
+      </x:c>
+      <x:c r="B21" s="8" t="str">
+        <x:v>study_context_end</x:v>
+      </x:c>
+      <x:c r="C21" s="8" t="str"/>
+      <x:c r="D21" s="8" t="str"/>
+      <x:c r="E21" s="8" t="str"/>
+      <x:c r="F21" s="8" t="str"/>
+      <x:c r="G21" s="8" t="str"/>
+      <x:c r="H21" s="8" t="str"/>
+      <x:c r="I21" s="8" t="str"/>
+      <x:c r="J21" s="8" t="str"/>
+      <x:c r="K21" s="8" t="str"/>
+      <x:c r="L21" s="8" t="str"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="8" t="str">
+        <x:v>begin group</x:v>
+      </x:c>
+      <x:c r="B22" s="8" t="str">
+        <x:v>credential_options</x:v>
+      </x:c>
+      <x:c r="C22" s="8" t="str">
+        <x:v>Credential security options</x:v>
+      </x:c>
+      <x:c r="D22" s="8" t="str"/>
+      <x:c r="E22" s="8" t="str"/>
+      <x:c r="F22" s="8" t="str"/>
+      <x:c r="G22" s="8" t="str"/>
+      <x:c r="H22" s="8" t="str"/>
+      <x:c r="I22" s="8" t="str"/>
+      <x:c r="J22" s="8" t="str">
+        <x:v>field-list</x:v>
+      </x:c>
+      <x:c r="K22" s="8" t="str"/>
+      <x:c r="L22" s="8" t="str"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="8" t="str">
+        <x:v>select_one pin_length</x:v>
+      </x:c>
+      <x:c r="B23" s="8" t="str">
+        <x:v>pin_length_input</x:v>
+      </x:c>
+      <x:c r="C23" s="8" t="str">
+        <x:v>PIN length</x:v>
+      </x:c>
+      <x:c r="D23" s="8" t="str">
+        <x:v>The PIN is entered only inside MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E23" s="8" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F23" s="8" t="str"/>
+      <x:c r="G23" s="8" t="str"/>
+      <x:c r="H23" s="8" t="str"/>
+      <x:c r="I23" s="8" t="str"/>
+      <x:c r="J23" s="8" t="str"/>
+      <x:c r="K23" s="8" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L23" s="8" t="str"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="8" t="str">
+        <x:v>select_one overwrite_policy</x:v>
+      </x:c>
+      <x:c r="B24" s="8" t="str">
+        <x:v>overwrite_policy_input</x:v>
+      </x:c>
+      <x:c r="C24" s="8" t="str">
+        <x:v>Existing card content</x:v>
+      </x:c>
+      <x:c r="D24" s="8" t="str">
+        <x:v>Use empty_only for new cards. Use replace only when intentionally replacing an existing credential.</x:v>
+      </x:c>
+      <x:c r="E24" s="8" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F24" s="8" t="str"/>
+      <x:c r="G24" s="8" t="str"/>
+      <x:c r="H24" s="8" t="str"/>
+      <x:c r="I24" s="8" t="str"/>
+      <x:c r="J24" s="8" t="str"/>
+      <x:c r="K24" s="8" t="str">
+        <x:v>empty_only</x:v>
+      </x:c>
+      <x:c r="L24" s="8" t="str"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="8" t="str">
+        <x:v>note</x:v>
+      </x:c>
+      <x:c r="B25" s="8" t="str">
+        <x:v>security_note</x:v>
+      </x:c>
+      <x:c r="C25" s="8" t="str">
+        <x:v>PIN and issuer-key handling</x:v>
+      </x:c>
+      <x:c r="D25" s="8" t="str">
+        <x:v>The PIN and private issuer key never return to ODK. The private signing key remains in Android Keystore.</x:v>
+      </x:c>
+      <x:c r="E25" s="8" t="str"/>
+      <x:c r="F25" s="8" t="str"/>
+      <x:c r="G25" s="8" t="str"/>
+      <x:c r="H25" s="8" t="str"/>
+      <x:c r="I25" s="8" t="str"/>
+      <x:c r="J25" s="8" t="str"/>
+      <x:c r="K25" s="8" t="str"/>
+      <x:c r="L25" s="8" t="str"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="8" t="str">
+        <x:v>end group</x:v>
+      </x:c>
+      <x:c r="B26" s="8" t="str">
+        <x:v>credential_options_end</x:v>
+      </x:c>
+      <x:c r="C26" s="8" t="str"/>
+      <x:c r="D26" s="8" t="str"/>
+      <x:c r="E26" s="8" t="str"/>
+      <x:c r="F26" s="8" t="str"/>
+      <x:c r="G26" s="8" t="str"/>
+      <x:c r="H26" s="8" t="str"/>
+      <x:c r="I26" s="8" t="str"/>
+      <x:c r="J26" s="8" t="str"/>
+      <x:c r="K26" s="8" t="str"/>
+      <x:c r="L26" s="8" t="str"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="8" t="str">
+        <x:v>begin group</x:v>
+      </x:c>
+      <x:c r="B27" s="8" t="str">
+        <x:v>run_nfc_credential_provisioning</x:v>
+      </x:c>
+      <x:c r="C27" s="8" t="str">
+        <x:v>Write and verify NFC credential</x:v>
+      </x:c>
+      <x:c r="D27" s="8" t="str">
+        <x:v>Complete provisioning in MethodMesh, then Commit to return here.</x:v>
+      </x:c>
+      <x:c r="E27" s="8" t="str"/>
+      <x:c r="F27" s="8" t="str"/>
+      <x:c r="G27" s="8" t="str"/>
+      <x:c r="H27" s="8" t="str"/>
+      <x:c r="I27" s="8" t="str"/>
+      <x:c r="J27" s="8" t="str">
+        <x:v>field-list</x:v>
+      </x:c>
+      <x:c r="K27" s="8" t="str"/>
+      <x:c r="L27" s="8" t="str">
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='nfc_credential_provisioning',input_credential_subject_id=${credential_subject_id_input},input_pin_length=${pin_length_input},input_overwrite_policy=${overwrite_policy_input},input_payload_mode='FULL',return_mode='flat')</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B28" s="8" t="str">
+        <x:v>methodmesh_execution_id</x:v>
+      </x:c>
+      <x:c r="C28" s="8" t="str">
+        <x:v>MethodMesh execution ID</x:v>
+      </x:c>
+      <x:c r="D28" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E28" s="8" t="str"/>
+      <x:c r="F28" s="8" t="str"/>
+      <x:c r="G28" s="8" t="str"/>
+      <x:c r="H28" s="8" t="str"/>
+      <x:c r="I28" s="8" t="str"/>
+      <x:c r="J28" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K28" s="8" t="str"/>
+      <x:c r="L28" s="8" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B29" s="8" t="str">
+        <x:v>methodmesh_status</x:v>
+      </x:c>
+      <x:c r="C29" s="8" t="str">
+        <x:v>MethodMesh status</x:v>
+      </x:c>
+      <x:c r="D29" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E29" s="8" t="str"/>
+      <x:c r="F29" s="8" t="str"/>
+      <x:c r="G29" s="8" t="str"/>
+      <x:c r="H29" s="8" t="str"/>
+      <x:c r="I29" s="8" t="str"/>
+      <x:c r="J29" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K29" s="8" t="str"/>
+      <x:c r="L29" s="8" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B30" s="8" t="str">
+        <x:v>credential_id</x:v>
+      </x:c>
+      <x:c r="C30" s="8" t="str">
+        <x:v>Credential ID</x:v>
+      </x:c>
+      <x:c r="D30" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E30" s="8" t="str"/>
+      <x:c r="F30" s="8" t="str"/>
+      <x:c r="G30" s="8" t="str"/>
+      <x:c r="H30" s="8" t="str"/>
+      <x:c r="I30" s="8" t="str"/>
+      <x:c r="J30" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K30" s="8" t="str"/>
+      <x:c r="L30" s="8" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B31" s="8" t="str">
+        <x:v>credential_subject_id</x:v>
+      </x:c>
+      <x:c r="C31" s="8" t="str">
+        <x:v>Credential subject ID returned</x:v>
+      </x:c>
+      <x:c r="D31" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E31" s="8" t="str"/>
+      <x:c r="F31" s="8" t="str"/>
+      <x:c r="G31" s="8" t="str"/>
+      <x:c r="H31" s="8" t="str"/>
+      <x:c r="I31" s="8" t="str"/>
+      <x:c r="J31" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K31" s="8" t="str"/>
+      <x:c r="L31" s="8" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="8" t="str">
+        <x:v>integer</x:v>
+      </x:c>
+      <x:c r="B32" s="8" t="str">
+        <x:v>pin_length</x:v>
+      </x:c>
+      <x:c r="C32" s="8" t="str">
+        <x:v>PIN length</x:v>
+      </x:c>
+      <x:c r="D32" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E32" s="8" t="str"/>
+      <x:c r="F32" s="8" t="str"/>
+      <x:c r="G32" s="8" t="str"/>
+      <x:c r="H32" s="8" t="str"/>
+      <x:c r="I32" s="8" t="str"/>
+      <x:c r="J32" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K32" s="8" t="str"/>
+      <x:c r="L32" s="8" t="str"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B33" s="8" t="str">
+        <x:v>credential_format_version</x:v>
+      </x:c>
+      <x:c r="C33" s="8" t="str">
+        <x:v>Credential format version</x:v>
+      </x:c>
+      <x:c r="D33" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E33" s="8" t="str"/>
+      <x:c r="F33" s="8" t="str"/>
+      <x:c r="G33" s="8" t="str"/>
+      <x:c r="H33" s="8" t="str"/>
+      <x:c r="I33" s="8" t="str"/>
+      <x:c r="J33" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K33" s="8" t="str"/>
+      <x:c r="L33" s="8" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B34" s="8" t="str">
+        <x:v>key_derivation</x:v>
+      </x:c>
+      <x:c r="C34" s="8" t="str">
+        <x:v>Key derivation</x:v>
+      </x:c>
+      <x:c r="D34" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E34" s="8" t="str"/>
+      <x:c r="F34" s="8" t="str"/>
+      <x:c r="G34" s="8" t="str"/>
+      <x:c r="H34" s="8" t="str"/>
+      <x:c r="I34" s="8" t="str"/>
+      <x:c r="J34" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K34" s="8" t="str"/>
+      <x:c r="L34" s="8" t="str"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B35" s="8" t="str">
+        <x:v>credential_issued_time_iso</x:v>
+      </x:c>
+      <x:c r="C35" s="8" t="str">
+        <x:v>Credential issued time</x:v>
+      </x:c>
+      <x:c r="D35" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E35" s="8" t="str"/>
+      <x:c r="F35" s="8" t="str"/>
+      <x:c r="G35" s="8" t="str"/>
+      <x:c r="H35" s="8" t="str"/>
+      <x:c r="I35" s="8" t="str"/>
+      <x:c r="J35" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K35" s="8" t="str"/>
+      <x:c r="L35" s="8" t="str"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B36" s="8" t="str">
+        <x:v>credential_envelope_hash</x:v>
+      </x:c>
+      <x:c r="C36" s="8" t="str">
+        <x:v>Credential envelope SHA-256</x:v>
+      </x:c>
+      <x:c r="D36" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E36" s="8" t="str"/>
+      <x:c r="F36" s="8" t="str"/>
+      <x:c r="G36" s="8" t="str"/>
+      <x:c r="H36" s="8" t="str"/>
+      <x:c r="I36" s="8" t="str"/>
+      <x:c r="J36" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K36" s="8" t="str"/>
+      <x:c r="L36" s="8" t="str"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B37" s="8" t="str">
+        <x:v>credential_secret_hash</x:v>
+      </x:c>
+      <x:c r="C37" s="8" t="str">
+        <x:v>Credential secret SHA-256</x:v>
+      </x:c>
+      <x:c r="D37" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E37" s="8" t="str"/>
+      <x:c r="F37" s="8" t="str"/>
+      <x:c r="G37" s="8" t="str"/>
+      <x:c r="H37" s="8" t="str"/>
+      <x:c r="I37" s="8" t="str"/>
+      <x:c r="J37" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K37" s="8" t="str"/>
+      <x:c r="L37" s="8" t="str"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B38" s="8" t="str">
+        <x:v>issuer_key_id</x:v>
+      </x:c>
+      <x:c r="C38" s="8" t="str">
+        <x:v>Issuer short key ID</x:v>
+      </x:c>
+      <x:c r="D38" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E38" s="8" t="str"/>
+      <x:c r="F38" s="8" t="str"/>
+      <x:c r="G38" s="8" t="str"/>
+      <x:c r="H38" s="8" t="str"/>
+      <x:c r="I38" s="8" t="str"/>
+      <x:c r="J38" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K38" s="8" t="str"/>
+      <x:c r="L38" s="8" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B39" s="8" t="str">
+        <x:v>issuer_public_key_fingerprint_sha256</x:v>
+      </x:c>
+      <x:c r="C39" s="8" t="str">
+        <x:v>Issuer public-key SHA-256 fingerprint</x:v>
+      </x:c>
+      <x:c r="D39" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E39" s="8" t="str"/>
+      <x:c r="F39" s="8" t="str"/>
+      <x:c r="G39" s="8" t="str"/>
+      <x:c r="H39" s="8" t="str"/>
+      <x:c r="I39" s="8" t="str"/>
+      <x:c r="J39" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K39" s="8" t="str"/>
+      <x:c r="L39" s="8" t="str"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B40" s="8" t="str">
+        <x:v>issuer_public_key_base64</x:v>
+      </x:c>
+      <x:c r="C40" s="8" t="str">
+        <x:v>Issuer public key</x:v>
+      </x:c>
+      <x:c r="D40" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E40" s="8" t="str"/>
+      <x:c r="F40" s="8" t="str"/>
+      <x:c r="G40" s="8" t="str"/>
+      <x:c r="H40" s="8" t="str"/>
+      <x:c r="I40" s="8" t="str"/>
+      <x:c r="J40" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K40" s="8" t="str"/>
+      <x:c r="L40" s="8" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B41" s="8" t="str">
+        <x:v>issuer_signature_algorithm</x:v>
+      </x:c>
+      <x:c r="C41" s="8" t="str">
+        <x:v>Issuer signature algorithm</x:v>
+      </x:c>
+      <x:c r="D41" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E41" s="8" t="str"/>
+      <x:c r="F41" s="8" t="str"/>
+      <x:c r="G41" s="8" t="str"/>
+      <x:c r="H41" s="8" t="str"/>
+      <x:c r="I41" s="8" t="str"/>
+      <x:c r="J41" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K41" s="8" t="str"/>
+      <x:c r="L41" s="8" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B42" s="8" t="str">
+        <x:v>provision_success</x:v>
+      </x:c>
+      <x:c r="C42" s="8" t="str">
+        <x:v>Provision success</x:v>
+      </x:c>
+      <x:c r="D42" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E42" s="8" t="str"/>
+      <x:c r="F42" s="8" t="str"/>
+      <x:c r="G42" s="8" t="str"/>
+      <x:c r="H42" s="8" t="str"/>
+      <x:c r="I42" s="8" t="str"/>
+      <x:c r="J42" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K42" s="8" t="str"/>
+      <x:c r="L42" s="8" t="str"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B43" s="8" t="str">
+        <x:v>provision_message</x:v>
+      </x:c>
+      <x:c r="C43" s="8" t="str">
+        <x:v>Provisioning result</x:v>
+      </x:c>
+      <x:c r="D43" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E43" s="8" t="str"/>
+      <x:c r="F43" s="8" t="str"/>
+      <x:c r="G43" s="8" t="str"/>
+      <x:c r="H43" s="8" t="str"/>
+      <x:c r="I43" s="8" t="str"/>
+      <x:c r="J43" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K43" s="8" t="str"/>
+      <x:c r="L43" s="8" t="str"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B44" s="8" t="str">
+        <x:v>provisioned_time_iso</x:v>
+      </x:c>
+      <x:c r="C44" s="8" t="str">
+        <x:v>Provisioned time</x:v>
+      </x:c>
+      <x:c r="D44" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E44" s="8" t="str"/>
+      <x:c r="F44" s="8" t="str"/>
+      <x:c r="G44" s="8" t="str"/>
+      <x:c r="H44" s="8" t="str"/>
+      <x:c r="I44" s="8" t="str"/>
+      <x:c r="J44" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K44" s="8" t="str"/>
+      <x:c r="L44" s="8" t="str"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B45" s="8" t="str">
+        <x:v>write_record_type</x:v>
+      </x:c>
+      <x:c r="C45" s="8" t="str">
+        <x:v>NFC write record type</x:v>
+      </x:c>
+      <x:c r="D45" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E45" s="8" t="str"/>
+      <x:c r="F45" s="8" t="str"/>
+      <x:c r="G45" s="8" t="str"/>
+      <x:c r="H45" s="8" t="str"/>
+      <x:c r="I45" s="8" t="str"/>
+      <x:c r="J45" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K45" s="8" t="str"/>
+      <x:c r="L45" s="8" t="str"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="8" t="str">
+        <x:v>integer</x:v>
+      </x:c>
+      <x:c r="B46" s="8" t="str">
+        <x:v>write_size_bytes</x:v>
+      </x:c>
+      <x:c r="C46" s="8" t="str">
+        <x:v>NFC write size (bytes)</x:v>
+      </x:c>
+      <x:c r="D46" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E46" s="8" t="str"/>
+      <x:c r="F46" s="8" t="str"/>
+      <x:c r="G46" s="8" t="str"/>
+      <x:c r="H46" s="8" t="str"/>
+      <x:c r="I46" s="8" t="str"/>
+      <x:c r="J46" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K46" s="8" t="str"/>
+      <x:c r="L46" s="8" t="str"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B47" s="8" t="str">
+        <x:v>overwrite_policy</x:v>
+      </x:c>
+      <x:c r="C47" s="8" t="str">
+        <x:v>Applied overwrite policy</x:v>
+      </x:c>
+      <x:c r="D47" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E47" s="8" t="str"/>
+      <x:c r="F47" s="8" t="str"/>
+      <x:c r="G47" s="8" t="str"/>
+      <x:c r="H47" s="8" t="str"/>
+      <x:c r="I47" s="8" t="str"/>
+      <x:c r="J47" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K47" s="8" t="str"/>
+      <x:c r="L47" s="8" t="str"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B48" s="8" t="str">
+        <x:v>previous_message_hash</x:v>
+      </x:c>
+      <x:c r="C48" s="8" t="str">
+        <x:v>Previous NFC message SHA-256</x:v>
+      </x:c>
+      <x:c r="D48" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E48" s="8" t="str"/>
+      <x:c r="F48" s="8" t="str"/>
+      <x:c r="G48" s="8" t="str"/>
+      <x:c r="H48" s="8" t="str"/>
+      <x:c r="I48" s="8" t="str"/>
+      <x:c r="J48" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K48" s="8" t="str"/>
+      <x:c r="L48" s="8" t="str"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B49" s="8" t="str">
+        <x:v>written_message_hash</x:v>
+      </x:c>
+      <x:c r="C49" s="8" t="str">
+        <x:v>Written NFC message SHA-256</x:v>
+      </x:c>
+      <x:c r="D49" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E49" s="8" t="str"/>
+      <x:c r="F49" s="8" t="str"/>
+      <x:c r="G49" s="8" t="str"/>
+      <x:c r="H49" s="8" t="str"/>
+      <x:c r="I49" s="8" t="str"/>
+      <x:c r="J49" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K49" s="8" t="str"/>
+      <x:c r="L49" s="8" t="str"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B50" s="8" t="str">
+        <x:v>write_verified</x:v>
+      </x:c>
+      <x:c r="C50" s="8" t="str">
+        <x:v>NFC write verified</x:v>
+      </x:c>
+      <x:c r="D50" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E50" s="8" t="str"/>
+      <x:c r="F50" s="8" t="str"/>
+      <x:c r="G50" s="8" t="str"/>
+      <x:c r="H50" s="8" t="str"/>
+      <x:c r="I50" s="8" t="str"/>
+      <x:c r="J50" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K50" s="8" t="str"/>
+      <x:c r="L50" s="8" t="str"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B51" s="8" t="str">
+        <x:v>tag_uid_hex</x:v>
+      </x:c>
+      <x:c r="C51" s="8" t="str">
+        <x:v>NFC tag UID</x:v>
+      </x:c>
+      <x:c r="D51" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E51" s="8" t="str"/>
+      <x:c r="F51" s="8" t="str"/>
+      <x:c r="G51" s="8" t="str"/>
+      <x:c r="H51" s="8" t="str"/>
+      <x:c r="I51" s="8" t="str"/>
+      <x:c r="J51" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K51" s="8" t="str"/>
+      <x:c r="L51" s="8" t="str"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B52" s="8" t="str">
+        <x:v>verification_evidence_hash</x:v>
+      </x:c>
+      <x:c r="C52" s="8" t="str">
+        <x:v>Verification evidence SHA-256</x:v>
+      </x:c>
+      <x:c r="D52" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E52" s="8" t="str"/>
+      <x:c r="F52" s="8" t="str"/>
+      <x:c r="G52" s="8" t="str"/>
+      <x:c r="H52" s="8" t="str"/>
+      <x:c r="I52" s="8" t="str"/>
+      <x:c r="J52" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K52" s="8" t="str"/>
+      <x:c r="L52" s="8" t="str"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B53" s="8" t="str">
+        <x:v>methodmesh_full_json</x:v>
+      </x:c>
+      <x:c r="C53" s="8" t="str">
+        <x:v>MethodMesh FULL JSON</x:v>
+      </x:c>
+      <x:c r="D53" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E53" s="8" t="str"/>
+      <x:c r="F53" s="8" t="str"/>
+      <x:c r="G53" s="8" t="str"/>
+      <x:c r="H53" s="8" t="str"/>
+      <x:c r="I53" s="8" t="str"/>
+      <x:c r="J53" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="K53" s="8" t="str"/>
+      <x:c r="L53" s="8" t="str"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="8" t="str">
+        <x:v>end group</x:v>
+      </x:c>
+      <x:c r="B54" s="8" t="str">
+        <x:v>run_nfc_credential_provisioning_end</x:v>
+      </x:c>
+      <x:c r="C54" s="8" t="str"/>
+      <x:c r="D54" s="8" t="str"/>
+      <x:c r="E54" s="8" t="str"/>
+      <x:c r="F54" s="8" t="str"/>
+      <x:c r="G54" s="8" t="str"/>
+      <x:c r="H54" s="8" t="str"/>
+      <x:c r="I54" s="8" t="str"/>
+      <x:c r="J54" s="8" t="str"/>
+      <x:c r="K54" s="8" t="str"/>
+      <x:c r="L54" s="8" t="str"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="8" t="str">
+        <x:v>note</x:v>
+      </x:c>
+      <x:c r="B55" s="8" t="str">
+        <x:v>provision_summary</x:v>
+      </x:c>
+      <x:c r="C55" s="8" t="str">
+        <x:v>Credential provisioning result</x:v>
+      </x:c>
+      <x:c r="D55" s="8" t="str">
+        <x:v>Credential ${credential_id}; write verified ${write_verified}; issuer ${issuer_key_id}; fingerprint ${issuer_public_key_fingerprint_sha256}.</x:v>
+      </x:c>
+      <x:c r="E55" s="8" t="str"/>
+      <x:c r="F55" s="8" t="str">
+        <x:v>${methodmesh_status} != ''</x:v>
+      </x:c>
+      <x:c r="G55" s="8" t="str"/>
+      <x:c r="H55" s="8" t="str"/>
+      <x:c r="I55" s="8" t="str"/>
+      <x:c r="J55" s="8" t="str"/>
+      <x:c r="K55" s="8" t="str"/>
+      <x:c r="L55" s="8" t="str"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="8" t="str">
+        <x:v>note</x:v>
+      </x:c>
+      <x:c r="B56" s="8" t="str">
+        <x:v>registry_architecture_note</x:v>
+      </x:c>
+      <x:c r="C56" s="8" t="str">
+        <x:v>Registry record retained</x:v>
+      </x:c>
+      <x:c r="D56" s="8" t="str">
+        <x:v>Name, role, site and administrative validity remain in ODK. The returned full issuer fingerprint is the value to place in the study's offline trusted-issuer configuration.</x:v>
+      </x:c>
+      <x:c r="E56" s="8" t="str"/>
+      <x:c r="F56" s="8" t="str"/>
+      <x:c r="G56" s="8" t="str"/>
+      <x:c r="H56" s="8" t="str"/>
+      <x:c r="I56" s="8" t="str"/>
+      <x:c r="J56" s="8" t="str"/>
+      <x:c r="K56" s="8" t="str"/>
+      <x:c r="L56" s="8" t="str"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="8"/>
+      <x:c r="B57" s="8"/>
+      <x:c r="C57" s="8"/>
+      <x:c r="D57" s="8"/>
+      <x:c r="E57" s="8"/>
+      <x:c r="F57" s="8"/>
+      <x:c r="G57" s="8"/>
+      <x:c r="H57" s="8"/>
+      <x:c r="I57" s="8"/>
+      <x:c r="J57" s="8"/>
+      <x:c r="K57" s="8"/>
+      <x:c r="L57" s="8"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="8"/>
+      <x:c r="B58" s="8"/>
+      <x:c r="C58" s="8"/>
+      <x:c r="D58" s="8"/>
+      <x:c r="E58" s="8"/>
+      <x:c r="F58" s="8"/>
+      <x:c r="G58" s="8"/>
+      <x:c r="H58" s="8"/>
+      <x:c r="I58" s="8"/>
+      <x:c r="J58" s="8"/>
+      <x:c r="K58" s="8"/>
+      <x:c r="L58" s="8"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="8"/>
+      <x:c r="B59" s="8"/>
+      <x:c r="C59" s="8"/>
+      <x:c r="D59" s="8"/>
+      <x:c r="E59" s="8"/>
+      <x:c r="F59" s="8"/>
+      <x:c r="G59" s="8"/>
+      <x:c r="H59" s="8"/>
+      <x:c r="I59" s="8"/>
+      <x:c r="J59" s="8"/>
+      <x:c r="K59" s="8"/>
+      <x:c r="L59" s="8"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="8"/>
+      <x:c r="B60" s="8"/>
+      <x:c r="C60" s="8"/>
+      <x:c r="D60" s="8"/>
+      <x:c r="E60" s="8"/>
+      <x:c r="F60" s="8"/>
+      <x:c r="G60" s="8"/>
+      <x:c r="H60" s="8"/>
+      <x:c r="I60" s="8"/>
+      <x:c r="J60" s="8"/>
+      <x:c r="K60" s="8"/>
+      <x:c r="L60" s="8"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="8"/>
+      <x:c r="B61" s="8"/>
+      <x:c r="C61" s="8"/>
+      <x:c r="D61" s="8"/>
+      <x:c r="E61" s="8"/>
+      <x:c r="F61" s="8"/>
+      <x:c r="G61" s="8"/>
+      <x:c r="H61" s="8"/>
+      <x:c r="I61" s="8"/>
+      <x:c r="J61" s="8"/>
+      <x:c r="K61" s="8"/>
+      <x:c r="L61" s="8"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="8"/>
+      <x:c r="B62" s="8"/>
+      <x:c r="C62" s="8"/>
+      <x:c r="D62" s="8"/>
+      <x:c r="E62" s="8"/>
+      <x:c r="F62" s="8"/>
+      <x:c r="G62" s="8"/>
+      <x:c r="H62" s="8"/>
+      <x:c r="I62" s="8"/>
+      <x:c r="J62" s="8"/>
+      <x:c r="K62" s="8"/>
+      <x:c r="L62" s="8"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="8"/>
+      <x:c r="B63" s="8"/>
+      <x:c r="C63" s="8"/>
+      <x:c r="D63" s="8"/>
+      <x:c r="E63" s="8"/>
+      <x:c r="F63" s="8"/>
+      <x:c r="G63" s="8"/>
+      <x:c r="H63" s="8"/>
+      <x:c r="I63" s="8"/>
+      <x:c r="J63" s="8"/>
+      <x:c r="K63" s="8"/>
+      <x:c r="L63" s="8"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="8"/>
+      <x:c r="B64" s="8"/>
+      <x:c r="C64" s="8"/>
+      <x:c r="D64" s="8"/>
+      <x:c r="E64" s="8"/>
+      <x:c r="F64" s="8"/>
+      <x:c r="G64" s="8"/>
+      <x:c r="H64" s="8"/>
+      <x:c r="I64" s="8"/>
+      <x:c r="J64" s="8"/>
+      <x:c r="K64" s="8"/>
+      <x:c r="L64" s="8"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="8"/>
+      <x:c r="B65" s="8"/>
+      <x:c r="C65" s="8"/>
+      <x:c r="D65" s="8"/>
+      <x:c r="E65" s="8"/>
+      <x:c r="F65" s="8"/>
+      <x:c r="G65" s="8"/>
+      <x:c r="H65" s="8"/>
+      <x:c r="I65" s="8"/>
+      <x:c r="J65" s="8"/>
+      <x:c r="K65" s="8"/>
+      <x:c r="L65" s="8"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="8"/>
+      <x:c r="B66" s="8"/>
+      <x:c r="C66" s="8"/>
+      <x:c r="D66" s="8"/>
+      <x:c r="E66" s="8"/>
+      <x:c r="F66" s="8"/>
+      <x:c r="G66" s="8"/>
+      <x:c r="H66" s="8"/>
+      <x:c r="I66" s="8"/>
+      <x:c r="J66" s="8"/>
+      <x:c r="K66" s="8"/>
+      <x:c r="L66" s="8"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="8"/>
+      <x:c r="B67" s="8"/>
+      <x:c r="C67" s="8"/>
+      <x:c r="D67" s="8"/>
+      <x:c r="E67" s="8"/>
+      <x:c r="F67" s="8"/>
+      <x:c r="G67" s="8"/>
+      <x:c r="H67" s="8"/>
+      <x:c r="I67" s="8"/>
+      <x:c r="J67" s="8"/>
+      <x:c r="K67" s="8"/>
+      <x:c r="L67" s="8"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="8"/>
+      <x:c r="B68" s="8"/>
+      <x:c r="C68" s="8"/>
+      <x:c r="D68" s="8"/>
+      <x:c r="E68" s="8"/>
+      <x:c r="F68" s="8"/>
+      <x:c r="G68" s="8"/>
+      <x:c r="H68" s="8"/>
+      <x:c r="I68" s="8"/>
+      <x:c r="J68" s="8"/>
+      <x:c r="K68" s="8"/>
+      <x:c r="L68" s="8"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="8"/>
+      <x:c r="B69" s="8"/>
+      <x:c r="C69" s="8"/>
+      <x:c r="D69" s="8"/>
+      <x:c r="E69" s="8"/>
+      <x:c r="F69" s="8"/>
+      <x:c r="G69" s="8"/>
+      <x:c r="H69" s="8"/>
+      <x:c r="I69" s="8"/>
+      <x:c r="J69" s="8"/>
+      <x:c r="K69" s="8"/>
+      <x:c r="L69" s="8"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="8"/>
+      <x:c r="B70" s="8"/>
+      <x:c r="C70" s="8"/>
+      <x:c r="D70" s="8"/>
+      <x:c r="E70" s="8"/>
+      <x:c r="F70" s="8"/>
+      <x:c r="G70" s="8"/>
+      <x:c r="H70" s="8"/>
+      <x:c r="I70" s="8"/>
+      <x:c r="J70" s="8"/>
+      <x:c r="K70" s="8"/>
+      <x:c r="L70" s="8"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="8"/>
+      <x:c r="B71" s="8"/>
+      <x:c r="C71" s="8"/>
+      <x:c r="D71" s="8"/>
+      <x:c r="E71" s="8"/>
+      <x:c r="F71" s="8"/>
+      <x:c r="G71" s="8"/>
+      <x:c r="H71" s="8"/>
+      <x:c r="I71" s="8"/>
+      <x:c r="J71" s="8"/>
+      <x:c r="K71" s="8"/>
+      <x:c r="L71" s="8"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="8"/>
+      <x:c r="B72" s="8"/>
+      <x:c r="C72" s="8"/>
+      <x:c r="D72" s="8"/>
+      <x:c r="E72" s="8"/>
+      <x:c r="F72" s="8"/>
+      <x:c r="G72" s="8"/>
+      <x:c r="H72" s="8"/>
+      <x:c r="I72" s="8"/>
+      <x:c r="J72" s="8"/>
+      <x:c r="K72" s="8"/>
+      <x:c r="L72" s="8"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="8"/>
+      <x:c r="B73" s="8"/>
+      <x:c r="C73" s="8"/>
+      <x:c r="D73" s="8"/>
+      <x:c r="E73" s="8"/>
+      <x:c r="F73" s="8"/>
+      <x:c r="G73" s="8"/>
+      <x:c r="H73" s="8"/>
+      <x:c r="I73" s="8"/>
+      <x:c r="J73" s="8"/>
+      <x:c r="K73" s="8"/>
+      <x:c r="L73" s="8"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="8"/>
+      <x:c r="B74" s="8"/>
+      <x:c r="C74" s="8"/>
+      <x:c r="D74" s="8"/>
+      <x:c r="E74" s="8"/>
+      <x:c r="F74" s="8"/>
+      <x:c r="G74" s="8"/>
+      <x:c r="H74" s="8"/>
+      <x:c r="I74" s="8"/>
+      <x:c r="J74" s="8"/>
+      <x:c r="K74" s="8"/>
+      <x:c r="L74" s="8"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="8"/>
+      <x:c r="B75" s="8"/>
+      <x:c r="C75" s="8"/>
+      <x:c r="D75" s="8"/>
+      <x:c r="E75" s="8"/>
+      <x:c r="F75" s="8"/>
+      <x:c r="G75" s="8"/>
+      <x:c r="H75" s="8"/>
+      <x:c r="I75" s="8"/>
+      <x:c r="J75" s="8"/>
+      <x:c r="K75" s="8"/>
+      <x:c r="L75" s="8"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="8"/>
+      <x:c r="B76" s="8"/>
+      <x:c r="C76" s="8"/>
+      <x:c r="D76" s="8"/>
+      <x:c r="E76" s="8"/>
+      <x:c r="F76" s="8"/>
+      <x:c r="G76" s="8"/>
+      <x:c r="H76" s="8"/>
+      <x:c r="I76" s="8"/>
+      <x:c r="J76" s="8"/>
+      <x:c r="K76" s="8"/>
+      <x:c r="L76" s="8"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="8"/>
+      <x:c r="B77" s="8"/>
+      <x:c r="C77" s="8"/>
+      <x:c r="D77" s="8"/>
+      <x:c r="E77" s="8"/>
+      <x:c r="F77" s="8"/>
+      <x:c r="G77" s="8"/>
+      <x:c r="H77" s="8"/>
+      <x:c r="I77" s="8"/>
+      <x:c r="J77" s="8"/>
+      <x:c r="K77" s="8"/>
+      <x:c r="L77" s="8"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="8"/>
+      <x:c r="B78" s="8"/>
+      <x:c r="C78" s="8"/>
+      <x:c r="D78" s="8"/>
+      <x:c r="E78" s="8"/>
+      <x:c r="F78" s="8"/>
+      <x:c r="G78" s="8"/>
+      <x:c r="H78" s="8"/>
+      <x:c r="I78" s="8"/>
+      <x:c r="J78" s="8"/>
+      <x:c r="K78" s="8"/>
+      <x:c r="L78" s="8"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="8"/>
+      <x:c r="B79" s="8"/>
+      <x:c r="C79" s="8"/>
+      <x:c r="D79" s="8"/>
+      <x:c r="E79" s="8"/>
+      <x:c r="F79" s="8"/>
+      <x:c r="G79" s="8"/>
+      <x:c r="H79" s="8"/>
+      <x:c r="I79" s="8"/>
+      <x:c r="J79" s="8"/>
+      <x:c r="K79" s="8"/>
+      <x:c r="L79" s="8"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="8"/>
+      <x:c r="B80" s="8"/>
+      <x:c r="C80" s="8"/>
+      <x:c r="D80" s="8"/>
+      <x:c r="E80" s="8"/>
+      <x:c r="F80" s="8"/>
+      <x:c r="G80" s="8"/>
+      <x:c r="H80" s="8"/>
+      <x:c r="I80" s="8"/>
+      <x:c r="J80" s="8"/>
+      <x:c r="K80" s="8"/>
+      <x:c r="L80" s="8"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="8"/>
+      <x:c r="B81" s="8"/>
+      <x:c r="C81" s="8"/>
+      <x:c r="D81" s="8"/>
+      <x:c r="E81" s="8"/>
+      <x:c r="F81" s="8"/>
+      <x:c r="G81" s="8"/>
+      <x:c r="H81" s="8"/>
+      <x:c r="I81" s="8"/>
+      <x:c r="J81" s="8"/>
+      <x:c r="K81" s="8"/>
+      <x:c r="L81" s="8"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="8"/>
+      <x:c r="B82" s="8"/>
+      <x:c r="C82" s="8"/>
+      <x:c r="D82" s="8"/>
+      <x:c r="E82" s="8"/>
+      <x:c r="F82" s="8"/>
+      <x:c r="G82" s="8"/>
+      <x:c r="H82" s="8"/>
+      <x:c r="I82" s="8"/>
+      <x:c r="J82" s="8"/>
+      <x:c r="K82" s="8"/>
+      <x:c r="L82" s="8"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="8"/>
+      <x:c r="B83" s="8"/>
+      <x:c r="C83" s="8"/>
+      <x:c r="D83" s="8"/>
+      <x:c r="E83" s="8"/>
+      <x:c r="F83" s="8"/>
+      <x:c r="G83" s="8"/>
+      <x:c r="H83" s="8"/>
+      <x:c r="I83" s="8"/>
+      <x:c r="J83" s="8"/>
+      <x:c r="K83" s="8"/>
+      <x:c r="L83" s="8"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="8"/>
+      <x:c r="B84" s="8"/>
+      <x:c r="C84" s="8"/>
+      <x:c r="D84" s="8"/>
+      <x:c r="E84" s="8"/>
+      <x:c r="F84" s="8"/>
+      <x:c r="G84" s="8"/>
+      <x:c r="H84" s="8"/>
+      <x:c r="I84" s="8"/>
+      <x:c r="J84" s="8"/>
+      <x:c r="K84" s="8"/>
+      <x:c r="L84" s="8"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="8"/>
+      <x:c r="B85" s="8"/>
+      <x:c r="C85" s="8"/>
+      <x:c r="D85" s="8"/>
+      <x:c r="E85" s="8"/>
+      <x:c r="F85" s="8"/>
+      <x:c r="G85" s="8"/>
+      <x:c r="H85" s="8"/>
+      <x:c r="I85" s="8"/>
+      <x:c r="J85" s="8"/>
+      <x:c r="K85" s="8"/>
+      <x:c r="L85" s="8"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="8"/>
+      <x:c r="B86" s="8"/>
+      <x:c r="C86" s="8"/>
+      <x:c r="D86" s="8"/>
+      <x:c r="E86" s="8"/>
+      <x:c r="F86" s="8"/>
+      <x:c r="G86" s="8"/>
+      <x:c r="H86" s="8"/>
+      <x:c r="I86" s="8"/>
+      <x:c r="J86" s="8"/>
+      <x:c r="K86" s="8"/>
+      <x:c r="L86" s="8"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="8"/>
+      <x:c r="B87" s="8"/>
+      <x:c r="C87" s="8"/>
+      <x:c r="D87" s="8"/>
+      <x:c r="E87" s="8"/>
+      <x:c r="F87" s="8"/>
+      <x:c r="G87" s="8"/>
+      <x:c r="H87" s="8"/>
+      <x:c r="I87" s="8"/>
+      <x:c r="J87" s="8"/>
+      <x:c r="K87" s="8"/>
+      <x:c r="L87" s="8"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="8"/>
+      <x:c r="B88" s="8"/>
+      <x:c r="C88" s="8"/>
+      <x:c r="D88" s="8"/>
+      <x:c r="E88" s="8"/>
+      <x:c r="F88" s="8"/>
+      <x:c r="G88" s="8"/>
+      <x:c r="H88" s="8"/>
+      <x:c r="I88" s="8"/>
+      <x:c r="J88" s="8"/>
+      <x:c r="K88" s="8"/>
+      <x:c r="L88" s="8"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="8"/>
+      <x:c r="B89" s="8"/>
+      <x:c r="C89" s="8"/>
+      <x:c r="D89" s="8"/>
+      <x:c r="E89" s="8"/>
+      <x:c r="F89" s="8"/>
+      <x:c r="G89" s="8"/>
+      <x:c r="H89" s="8"/>
+      <x:c r="I89" s="8"/>
+      <x:c r="J89" s="8"/>
+      <x:c r="K89" s="8"/>
+      <x:c r="L89" s="8"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="8"/>
+      <x:c r="B90" s="8"/>
+      <x:c r="C90" s="8"/>
+      <x:c r="D90" s="8"/>
+      <x:c r="E90" s="8"/>
+      <x:c r="F90" s="8"/>
+      <x:c r="G90" s="8"/>
+      <x:c r="H90" s="8"/>
+      <x:c r="I90" s="8"/>
+      <x:c r="J90" s="8"/>
+      <x:c r="K90" s="8"/>
+      <x:c r="L90" s="8"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="8"/>
+      <x:c r="B91" s="8"/>
+      <x:c r="C91" s="8"/>
+      <x:c r="D91" s="8"/>
+      <x:c r="E91" s="8"/>
+      <x:c r="F91" s="8"/>
+      <x:c r="G91" s="8"/>
+      <x:c r="H91" s="8"/>
+      <x:c r="I91" s="8"/>
+      <x:c r="J91" s="8"/>
+      <x:c r="K91" s="8"/>
+      <x:c r="L91" s="8"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="8"/>
+      <x:c r="B92" s="8"/>
+      <x:c r="C92" s="8"/>
+      <x:c r="D92" s="8"/>
+      <x:c r="E92" s="8"/>
+      <x:c r="F92" s="8"/>
+      <x:c r="G92" s="8"/>
+      <x:c r="H92" s="8"/>
+      <x:c r="I92" s="8"/>
+      <x:c r="J92" s="8"/>
+      <x:c r="K92" s="8"/>
+      <x:c r="L92" s="8"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="8"/>
+      <x:c r="B93" s="8"/>
+      <x:c r="C93" s="8"/>
+      <x:c r="D93" s="8"/>
+      <x:c r="E93" s="8"/>
+      <x:c r="F93" s="8"/>
+      <x:c r="G93" s="8"/>
+      <x:c r="H93" s="8"/>
+      <x:c r="I93" s="8"/>
+      <x:c r="J93" s="8"/>
+      <x:c r="K93" s="8"/>
+      <x:c r="L93" s="8"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="8"/>
+      <x:c r="B94" s="8"/>
+      <x:c r="C94" s="8"/>
+      <x:c r="D94" s="8"/>
+      <x:c r="E94" s="8"/>
+      <x:c r="F94" s="8"/>
+      <x:c r="G94" s="8"/>
+      <x:c r="H94" s="8"/>
+      <x:c r="I94" s="8"/>
+      <x:c r="J94" s="8"/>
+      <x:c r="K94" s="8"/>
+      <x:c r="L94" s="8"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="8"/>
+      <x:c r="B95" s="8"/>
+      <x:c r="C95" s="8"/>
+      <x:c r="D95" s="8"/>
+      <x:c r="E95" s="8"/>
+      <x:c r="F95" s="8"/>
+      <x:c r="G95" s="8"/>
+      <x:c r="H95" s="8"/>
+      <x:c r="I95" s="8"/>
+      <x:c r="J95" s="8"/>
+      <x:c r="K95" s="8"/>
+      <x:c r="L95" s="8"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="8"/>
+      <x:c r="B96" s="8"/>
+      <x:c r="C96" s="8"/>
+      <x:c r="D96" s="8"/>
+      <x:c r="E96" s="8"/>
+      <x:c r="F96" s="8"/>
+      <x:c r="G96" s="8"/>
+      <x:c r="H96" s="8"/>
+      <x:c r="I96" s="8"/>
+      <x:c r="J96" s="8"/>
+      <x:c r="K96" s="8"/>
+      <x:c r="L96" s="8"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="8"/>
+      <x:c r="B97" s="8"/>
+      <x:c r="C97" s="8"/>
+      <x:c r="D97" s="8"/>
+      <x:c r="E97" s="8"/>
+      <x:c r="F97" s="8"/>
+      <x:c r="G97" s="8"/>
+      <x:c r="H97" s="8"/>
+      <x:c r="I97" s="8"/>
+      <x:c r="J97" s="8"/>
+      <x:c r="K97" s="8"/>
+      <x:c r="L97" s="8"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="8"/>
+      <x:c r="B98" s="8"/>
+      <x:c r="C98" s="8"/>
+      <x:c r="D98" s="8"/>
+      <x:c r="E98" s="8"/>
+      <x:c r="F98" s="8"/>
+      <x:c r="G98" s="8"/>
+      <x:c r="H98" s="8"/>
+      <x:c r="I98" s="8"/>
+      <x:c r="J98" s="8"/>
+      <x:c r="K98" s="8"/>
+      <x:c r="L98" s="8"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="8"/>
+      <x:c r="B99" s="8"/>
+      <x:c r="C99" s="8"/>
+      <x:c r="D99" s="8"/>
+      <x:c r="E99" s="8"/>
+      <x:c r="F99" s="8"/>
+      <x:c r="G99" s="8"/>
+      <x:c r="H99" s="8"/>
+      <x:c r="I99" s="8"/>
+      <x:c r="J99" s="8"/>
+      <x:c r="K99" s="8"/>
+      <x:c r="L99" s="8"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="8"/>
+      <x:c r="B100" s="8"/>
+      <x:c r="C100" s="8"/>
+      <x:c r="D100" s="8"/>
+      <x:c r="E100" s="8"/>
+      <x:c r="F100" s="8"/>
+      <x:c r="G100" s="8"/>
+      <x:c r="H100" s="8"/>
+      <x:c r="I100" s="8"/>
+      <x:c r="J100" s="8"/>
+      <x:c r="K100" s="8"/>
+      <x:c r="L100" s="8"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="8"/>
+      <x:c r="B101" s="8"/>
+      <x:c r="C101" s="8"/>
+      <x:c r="D101" s="8"/>
+      <x:c r="E101" s="8"/>
+      <x:c r="F101" s="8"/>
+      <x:c r="G101" s="8"/>
+      <x:c r="H101" s="8"/>
+      <x:c r="I101" s="8"/>
+      <x:c r="J101" s="8"/>
+      <x:c r="K101" s="8"/>
+      <x:c r="L101" s="8"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="8"/>
+      <x:c r="B102" s="8"/>
+      <x:c r="C102" s="8"/>
+      <x:c r="D102" s="8"/>
+      <x:c r="E102" s="8"/>
+      <x:c r="F102" s="8"/>
+      <x:c r="G102" s="8"/>
+      <x:c r="H102" s="8"/>
+      <x:c r="I102" s="8"/>
+      <x:c r="J102" s="8"/>
+      <x:c r="K102" s="8"/>
+      <x:c r="L102" s="8"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="8"/>
+      <x:c r="B103" s="8"/>
+      <x:c r="C103" s="8"/>
+      <x:c r="D103" s="8"/>
+      <x:c r="E103" s="8"/>
+      <x:c r="F103" s="8"/>
+      <x:c r="G103" s="8"/>
+      <x:c r="H103" s="8"/>
+      <x:c r="I103" s="8"/>
+      <x:c r="J103" s="8"/>
+      <x:c r="K103" s="8"/>
+      <x:c r="L103" s="8"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="8"/>
+      <x:c r="B104" s="8"/>
+      <x:c r="C104" s="8"/>
+      <x:c r="D104" s="8"/>
+      <x:c r="E104" s="8"/>
+      <x:c r="F104" s="8"/>
+      <x:c r="G104" s="8"/>
+      <x:c r="H104" s="8"/>
+      <x:c r="I104" s="8"/>
+      <x:c r="J104" s="8"/>
+      <x:c r="K104" s="8"/>
+      <x:c r="L104" s="8"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="8"/>
+      <x:c r="B105" s="8"/>
+      <x:c r="C105" s="8"/>
+      <x:c r="D105" s="8"/>
+      <x:c r="E105" s="8"/>
+      <x:c r="F105" s="8"/>
+      <x:c r="G105" s="8"/>
+      <x:c r="H105" s="8"/>
+      <x:c r="I105" s="8"/>
+      <x:c r="J105" s="8"/>
+      <x:c r="K105" s="8"/>
+      <x:c r="L105" s="8"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="8"/>
+      <x:c r="B106" s="8"/>
+      <x:c r="C106" s="8"/>
+      <x:c r="D106" s="8"/>
+      <x:c r="E106" s="8"/>
+      <x:c r="F106" s="8"/>
+      <x:c r="G106" s="8"/>
+      <x:c r="H106" s="8"/>
+      <x:c r="I106" s="8"/>
+      <x:c r="J106" s="8"/>
+      <x:c r="K106" s="8"/>
+      <x:c r="L106" s="8"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="8"/>
+      <x:c r="B107" s="8"/>
+      <x:c r="C107" s="8"/>
+      <x:c r="D107" s="8"/>
+      <x:c r="E107" s="8"/>
+      <x:c r="F107" s="8"/>
+      <x:c r="G107" s="8"/>
+      <x:c r="H107" s="8"/>
+      <x:c r="I107" s="8"/>
+      <x:c r="J107" s="8"/>
+      <x:c r="K107" s="8"/>
+      <x:c r="L107" s="8"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="8"/>
+      <x:c r="B108" s="8"/>
+      <x:c r="C108" s="8"/>
+      <x:c r="D108" s="8"/>
+      <x:c r="E108" s="8"/>
+      <x:c r="F108" s="8"/>
+      <x:c r="G108" s="8"/>
+      <x:c r="H108" s="8"/>
+      <x:c r="I108" s="8"/>
+      <x:c r="J108" s="8"/>
+      <x:c r="K108" s="8"/>
+      <x:c r="L108" s="8"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="8"/>
+      <x:c r="B109" s="8"/>
+      <x:c r="C109" s="8"/>
+      <x:c r="D109" s="8"/>
+      <x:c r="E109" s="8"/>
+      <x:c r="F109" s="8"/>
+      <x:c r="G109" s="8"/>
+      <x:c r="H109" s="8"/>
+      <x:c r="I109" s="8"/>
+      <x:c r="J109" s="8"/>
+      <x:c r="K109" s="8"/>
+      <x:c r="L109" s="8"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="8"/>
+      <x:c r="B110" s="8"/>
+      <x:c r="C110" s="8"/>
+      <x:c r="D110" s="8"/>
+      <x:c r="E110" s="8"/>
+      <x:c r="F110" s="8"/>
+      <x:c r="G110" s="8"/>
+      <x:c r="H110" s="8"/>
+      <x:c r="I110" s="8"/>
+      <x:c r="J110" s="8"/>
+      <x:c r="K110" s="8"/>
+      <x:c r="L110" s="8"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="8"/>
+      <x:c r="B111" s="8"/>
+      <x:c r="C111" s="8"/>
+      <x:c r="D111" s="8"/>
+      <x:c r="E111" s="8"/>
+      <x:c r="F111" s="8"/>
+      <x:c r="G111" s="8"/>
+      <x:c r="H111" s="8"/>
+      <x:c r="I111" s="8"/>
+      <x:c r="J111" s="8"/>
+      <x:c r="K111" s="8"/>
+      <x:c r="L111" s="8"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="8"/>
+      <x:c r="B112" s="8"/>
+      <x:c r="C112" s="8"/>
+      <x:c r="D112" s="8"/>
+      <x:c r="E112" s="8"/>
+      <x:c r="F112" s="8"/>
+      <x:c r="G112" s="8"/>
+      <x:c r="H112" s="8"/>
+      <x:c r="I112" s="8"/>
+      <x:c r="J112" s="8"/>
+      <x:c r="K112" s="8"/>
+      <x:c r="L112" s="8"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="8"/>
+      <x:c r="B113" s="8"/>
+      <x:c r="C113" s="8"/>
+      <x:c r="D113" s="8"/>
+      <x:c r="E113" s="8"/>
+      <x:c r="F113" s="8"/>
+      <x:c r="G113" s="8"/>
+      <x:c r="H113" s="8"/>
+      <x:c r="I113" s="8"/>
+      <x:c r="J113" s="8"/>
+      <x:c r="K113" s="8"/>
+      <x:c r="L113" s="8"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="8"/>
+      <x:c r="B114" s="8"/>
+      <x:c r="C114" s="8"/>
+      <x:c r="D114" s="8"/>
+      <x:c r="E114" s="8"/>
+      <x:c r="F114" s="8"/>
+      <x:c r="G114" s="8"/>
+      <x:c r="H114" s="8"/>
+      <x:c r="I114" s="8"/>
+      <x:c r="J114" s="8"/>
+      <x:c r="K114" s="8"/>
+      <x:c r="L114" s="8"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="8"/>
+      <x:c r="B115" s="8"/>
+      <x:c r="C115" s="8"/>
+      <x:c r="D115" s="8"/>
+      <x:c r="E115" s="8"/>
+      <x:c r="F115" s="8"/>
+      <x:c r="G115" s="8"/>
+      <x:c r="H115" s="8"/>
+      <x:c r="I115" s="8"/>
+      <x:c r="J115" s="8"/>
+      <x:c r="K115" s="8"/>
+      <x:c r="L115" s="8"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="8"/>
+      <x:c r="B116" s="8"/>
+      <x:c r="C116" s="8"/>
+      <x:c r="D116" s="8"/>
+      <x:c r="E116" s="8"/>
+      <x:c r="F116" s="8"/>
+      <x:c r="G116" s="8"/>
+      <x:c r="H116" s="8"/>
+      <x:c r="I116" s="8"/>
+      <x:c r="J116" s="8"/>
+      <x:c r="K116" s="8"/>
+      <x:c r="L116" s="8"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="8"/>
+      <x:c r="B117" s="8"/>
+      <x:c r="C117" s="8"/>
+      <x:c r="D117" s="8"/>
+      <x:c r="E117" s="8"/>
+      <x:c r="F117" s="8"/>
+      <x:c r="G117" s="8"/>
+      <x:c r="H117" s="8"/>
+      <x:c r="I117" s="8"/>
+      <x:c r="J117" s="8"/>
+      <x:c r="K117" s="8"/>
+      <x:c r="L117" s="8"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="8"/>
+      <x:c r="B118" s="8"/>
+      <x:c r="C118" s="8"/>
+      <x:c r="D118" s="8"/>
+      <x:c r="E118" s="8"/>
+      <x:c r="F118" s="8"/>
+      <x:c r="G118" s="8"/>
+      <x:c r="H118" s="8"/>
+      <x:c r="I118" s="8"/>
+      <x:c r="J118" s="8"/>
+      <x:c r="K118" s="8"/>
+      <x:c r="L118" s="8"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="8"/>
+      <x:c r="B119" s="8"/>
+      <x:c r="C119" s="8"/>
+      <x:c r="D119" s="8"/>
+      <x:c r="E119" s="8"/>
+      <x:c r="F119" s="8"/>
+      <x:c r="G119" s="8"/>
+      <x:c r="H119" s="8"/>
+      <x:c r="I119" s="8"/>
+      <x:c r="J119" s="8"/>
+      <x:c r="K119" s="8"/>
+      <x:c r="L119" s="8"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="8"/>
+      <x:c r="B120" s="8"/>
+      <x:c r="C120" s="8"/>
+      <x:c r="D120" s="8"/>
+      <x:c r="E120" s="8"/>
+      <x:c r="F120" s="8"/>
+      <x:c r="G120" s="8"/>
+      <x:c r="H120" s="8"/>
+      <x:c r="I120" s="8"/>
+      <x:c r="J120" s="8"/>
+      <x:c r="K120" s="8"/>
+      <x:c r="L120" s="8"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="8"/>
+      <x:c r="B121" s="8"/>
+      <x:c r="C121" s="8"/>
+      <x:c r="D121" s="8"/>
+      <x:c r="E121" s="8"/>
+      <x:c r="F121" s="8"/>
+      <x:c r="G121" s="8"/>
+      <x:c r="H121" s="8"/>
+      <x:c r="I121" s="8"/>
+      <x:c r="J121" s="8"/>
+      <x:c r="K121" s="8"/>
+      <x:c r="L121" s="8"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="8"/>
+      <x:c r="B122" s="8"/>
+      <x:c r="C122" s="8"/>
+      <x:c r="D122" s="8"/>
+      <x:c r="E122" s="8"/>
+      <x:c r="F122" s="8"/>
+      <x:c r="G122" s="8"/>
+      <x:c r="H122" s="8"/>
+      <x:c r="I122" s="8"/>
+      <x:c r="J122" s="8"/>
+      <x:c r="K122" s="8"/>
+      <x:c r="L122" s="8"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="8"/>
+      <x:c r="B123" s="8"/>
+      <x:c r="C123" s="8"/>
+      <x:c r="D123" s="8"/>
+      <x:c r="E123" s="8"/>
+      <x:c r="F123" s="8"/>
+      <x:c r="G123" s="8"/>
+      <x:c r="H123" s="8"/>
+      <x:c r="I123" s="8"/>
+      <x:c r="J123" s="8"/>
+      <x:c r="K123" s="8"/>
+      <x:c r="L123" s="8"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="8"/>
+      <x:c r="B124" s="8"/>
+      <x:c r="C124" s="8"/>
+      <x:c r="D124" s="8"/>
+      <x:c r="E124" s="8"/>
+      <x:c r="F124" s="8"/>
+      <x:c r="G124" s="8"/>
+      <x:c r="H124" s="8"/>
+      <x:c r="I124" s="8"/>
+      <x:c r="J124" s="8"/>
+      <x:c r="K124" s="8"/>
+      <x:c r="L124" s="8"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="8"/>
+      <x:c r="B125" s="8"/>
+      <x:c r="C125" s="8"/>
+      <x:c r="D125" s="8"/>
+      <x:c r="E125" s="8"/>
+      <x:c r="F125" s="8"/>
+      <x:c r="G125" s="8"/>
+      <x:c r="H125" s="8"/>
+      <x:c r="I125" s="8"/>
+      <x:c r="J125" s="8"/>
+      <x:c r="K125" s="8"/>
+      <x:c r="L125" s="8"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" s="8"/>
+      <x:c r="B126" s="8"/>
+      <x:c r="C126" s="8"/>
+      <x:c r="D126" s="8"/>
+      <x:c r="E126" s="8"/>
+      <x:c r="F126" s="8"/>
+      <x:c r="G126" s="8"/>
+      <x:c r="H126" s="8"/>
+      <x:c r="I126" s="8"/>
+      <x:c r="J126" s="8"/>
+      <x:c r="K126" s="8"/>
+      <x:c r="L126" s="8"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" s="8"/>
+      <x:c r="B127" s="8"/>
+      <x:c r="C127" s="8"/>
+      <x:c r="D127" s="8"/>
+      <x:c r="E127" s="8"/>
+      <x:c r="F127" s="8"/>
+      <x:c r="G127" s="8"/>
+      <x:c r="H127" s="8"/>
+      <x:c r="I127" s="8"/>
+      <x:c r="J127" s="8"/>
+      <x:c r="K127" s="8"/>
+      <x:c r="L127" s="8"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="8"/>
+      <x:c r="B128" s="8"/>
+      <x:c r="C128" s="8"/>
+      <x:c r="D128" s="8"/>
+      <x:c r="E128" s="8"/>
+      <x:c r="F128" s="8"/>
+      <x:c r="G128" s="8"/>
+      <x:c r="H128" s="8"/>
+      <x:c r="I128" s="8"/>
+      <x:c r="J128" s="8"/>
+      <x:c r="K128" s="8"/>
+      <x:c r="L128" s="8"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" s="8"/>
+      <x:c r="B129" s="8"/>
+      <x:c r="C129" s="8"/>
+      <x:c r="D129" s="8"/>
+      <x:c r="E129" s="8"/>
+      <x:c r="F129" s="8"/>
+      <x:c r="G129" s="8"/>
+      <x:c r="H129" s="8"/>
+      <x:c r="I129" s="8"/>
+      <x:c r="J129" s="8"/>
+      <x:c r="K129" s="8"/>
+      <x:c r="L129" s="8"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" s="8"/>
+      <x:c r="B130" s="8"/>
+      <x:c r="C130" s="8"/>
+      <x:c r="D130" s="8"/>
+      <x:c r="E130" s="8"/>
+      <x:c r="F130" s="8"/>
+      <x:c r="G130" s="8"/>
+      <x:c r="H130" s="8"/>
+      <x:c r="I130" s="8"/>
+      <x:c r="J130" s="8"/>
+      <x:c r="K130" s="8"/>
+      <x:c r="L130" s="8"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" s="8"/>
+      <x:c r="B131" s="8"/>
+      <x:c r="C131" s="8"/>
+      <x:c r="D131" s="8"/>
+      <x:c r="E131" s="8"/>
+      <x:c r="F131" s="8"/>
+      <x:c r="G131" s="8"/>
+      <x:c r="H131" s="8"/>
+      <x:c r="I131" s="8"/>
+      <x:c r="J131" s="8"/>
+      <x:c r="K131" s="8"/>
+      <x:c r="L131" s="8"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="8"/>
+      <x:c r="B132" s="8"/>
+      <x:c r="C132" s="8"/>
+      <x:c r="D132" s="8"/>
+      <x:c r="E132" s="8"/>
+      <x:c r="F132" s="8"/>
+      <x:c r="G132" s="8"/>
+      <x:c r="H132" s="8"/>
+      <x:c r="I132" s="8"/>
+      <x:c r="J132" s="8"/>
+      <x:c r="K132" s="8"/>
+      <x:c r="L132" s="8"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="8"/>
+      <x:c r="B133" s="8"/>
+      <x:c r="C133" s="8"/>
+      <x:c r="D133" s="8"/>
+      <x:c r="E133" s="8"/>
+      <x:c r="F133" s="8"/>
+      <x:c r="G133" s="8"/>
+      <x:c r="H133" s="8"/>
+      <x:c r="I133" s="8"/>
+      <x:c r="J133" s="8"/>
+      <x:c r="K133" s="8"/>
+      <x:c r="L133" s="8"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" s="8"/>
+      <x:c r="B134" s="8"/>
+      <x:c r="C134" s="8"/>
+      <x:c r="D134" s="8"/>
+      <x:c r="E134" s="8"/>
+      <x:c r="F134" s="8"/>
+      <x:c r="G134" s="8"/>
+      <x:c r="H134" s="8"/>
+      <x:c r="I134" s="8"/>
+      <x:c r="J134" s="8"/>
+      <x:c r="K134" s="8"/>
+      <x:c r="L134" s="8"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" s="8"/>
+      <x:c r="B135" s="8"/>
+      <x:c r="C135" s="8"/>
+      <x:c r="D135" s="8"/>
+      <x:c r="E135" s="8"/>
+      <x:c r="F135" s="8"/>
+      <x:c r="G135" s="8"/>
+      <x:c r="H135" s="8"/>
+      <x:c r="I135" s="8"/>
+      <x:c r="J135" s="8"/>
+      <x:c r="K135" s="8"/>
+      <x:c r="L135" s="8"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" s="8"/>
+      <x:c r="B136" s="8"/>
+      <x:c r="C136" s="8"/>
+      <x:c r="D136" s="8"/>
+      <x:c r="E136" s="8"/>
+      <x:c r="F136" s="8"/>
+      <x:c r="G136" s="8"/>
+      <x:c r="H136" s="8"/>
+      <x:c r="I136" s="8"/>
+      <x:c r="J136" s="8"/>
+      <x:c r="K136" s="8"/>
+      <x:c r="L136" s="8"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" s="8"/>
+      <x:c r="B137" s="8"/>
+      <x:c r="C137" s="8"/>
+      <x:c r="D137" s="8"/>
+      <x:c r="E137" s="8"/>
+      <x:c r="F137" s="8"/>
+      <x:c r="G137" s="8"/>
+      <x:c r="H137" s="8"/>
+      <x:c r="I137" s="8"/>
+      <x:c r="J137" s="8"/>
+      <x:c r="K137" s="8"/>
+      <x:c r="L137" s="8"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" s="8"/>
+      <x:c r="B138" s="8"/>
+      <x:c r="C138" s="8"/>
+      <x:c r="D138" s="8"/>
+      <x:c r="E138" s="8"/>
+      <x:c r="F138" s="8"/>
+      <x:c r="G138" s="8"/>
+      <x:c r="H138" s="8"/>
+      <x:c r="I138" s="8"/>
+      <x:c r="J138" s="8"/>
+      <x:c r="K138" s="8"/>
+      <x:c r="L138" s="8"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" s="8"/>
+      <x:c r="B139" s="8"/>
+      <x:c r="C139" s="8"/>
+      <x:c r="D139" s="8"/>
+      <x:c r="E139" s="8"/>
+      <x:c r="F139" s="8"/>
+      <x:c r="G139" s="8"/>
+      <x:c r="H139" s="8"/>
+      <x:c r="I139" s="8"/>
+      <x:c r="J139" s="8"/>
+      <x:c r="K139" s="8"/>
+      <x:c r="L139" s="8"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" s="8"/>
+      <x:c r="B140" s="8"/>
+      <x:c r="C140" s="8"/>
+      <x:c r="D140" s="8"/>
+      <x:c r="E140" s="8"/>
+      <x:c r="F140" s="8"/>
+      <x:c r="G140" s="8"/>
+      <x:c r="H140" s="8"/>
+      <x:c r="I140" s="8"/>
+      <x:c r="J140" s="8"/>
+      <x:c r="K140" s="8"/>
+      <x:c r="L140" s="8"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" s="8"/>
+      <x:c r="B141" s="8"/>
+      <x:c r="C141" s="8"/>
+      <x:c r="D141" s="8"/>
+      <x:c r="E141" s="8"/>
+      <x:c r="F141" s="8"/>
+      <x:c r="G141" s="8"/>
+      <x:c r="H141" s="8"/>
+      <x:c r="I141" s="8"/>
+      <x:c r="J141" s="8"/>
+      <x:c r="K141" s="8"/>
+      <x:c r="L141" s="8"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" s="8"/>
+      <x:c r="B142" s="8"/>
+      <x:c r="C142" s="8"/>
+      <x:c r="D142" s="8"/>
+      <x:c r="E142" s="8"/>
+      <x:c r="F142" s="8"/>
+      <x:c r="G142" s="8"/>
+      <x:c r="H142" s="8"/>
+      <x:c r="I142" s="8"/>
+      <x:c r="J142" s="8"/>
+      <x:c r="K142" s="8"/>
+      <x:c r="L142" s="8"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" s="8"/>
+      <x:c r="B143" s="8"/>
+      <x:c r="C143" s="8"/>
+      <x:c r="D143" s="8"/>
+      <x:c r="E143" s="8"/>
+      <x:c r="F143" s="8"/>
+      <x:c r="G143" s="8"/>
+      <x:c r="H143" s="8"/>
+      <x:c r="I143" s="8"/>
+      <x:c r="J143" s="8"/>
+      <x:c r="K143" s="8"/>
+      <x:c r="L143" s="8"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" s="8"/>
+      <x:c r="B144" s="8"/>
+      <x:c r="C144" s="8"/>
+      <x:c r="D144" s="8"/>
+      <x:c r="E144" s="8"/>
+      <x:c r="F144" s="8"/>
+      <x:c r="G144" s="8"/>
+      <x:c r="H144" s="8"/>
+      <x:c r="I144" s="8"/>
+      <x:c r="J144" s="8"/>
+      <x:c r="K144" s="8"/>
+      <x:c r="L144" s="8"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" s="8"/>
+      <x:c r="B145" s="8"/>
+      <x:c r="C145" s="8"/>
+      <x:c r="D145" s="8"/>
+      <x:c r="E145" s="8"/>
+      <x:c r="F145" s="8"/>
+      <x:c r="G145" s="8"/>
+      <x:c r="H145" s="8"/>
+      <x:c r="I145" s="8"/>
+      <x:c r="J145" s="8"/>
+      <x:c r="K145" s="8"/>
+      <x:c r="L145" s="8"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" s="8"/>
+      <x:c r="B146" s="8"/>
+      <x:c r="C146" s="8"/>
+      <x:c r="D146" s="8"/>
+      <x:c r="E146" s="8"/>
+      <x:c r="F146" s="8"/>
+      <x:c r="G146" s="8"/>
+      <x:c r="H146" s="8"/>
+      <x:c r="I146" s="8"/>
+      <x:c r="J146" s="8"/>
+      <x:c r="K146" s="8"/>
+      <x:c r="L146" s="8"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" s="8"/>
+      <x:c r="B147" s="8"/>
+      <x:c r="C147" s="8"/>
+      <x:c r="D147" s="8"/>
+      <x:c r="E147" s="8"/>
+      <x:c r="F147" s="8"/>
+      <x:c r="G147" s="8"/>
+      <x:c r="H147" s="8"/>
+      <x:c r="I147" s="8"/>
+      <x:c r="J147" s="8"/>
+      <x:c r="K147" s="8"/>
+      <x:c r="L147" s="8"/>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" s="8"/>
+      <x:c r="B148" s="8"/>
+      <x:c r="C148" s="8"/>
+      <x:c r="D148" s="8"/>
+      <x:c r="E148" s="8"/>
+      <x:c r="F148" s="8"/>
+      <x:c r="G148" s="8"/>
+      <x:c r="H148" s="8"/>
+      <x:c r="I148" s="8"/>
+      <x:c r="J148" s="8"/>
+      <x:c r="K148" s="8"/>
+      <x:c r="L148" s="8"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" s="8"/>
+      <x:c r="B149" s="8"/>
+      <x:c r="C149" s="8"/>
+      <x:c r="D149" s="8"/>
+      <x:c r="E149" s="8"/>
+      <x:c r="F149" s="8"/>
+      <x:c r="G149" s="8"/>
+      <x:c r="H149" s="8"/>
+      <x:c r="I149" s="8"/>
+      <x:c r="J149" s="8"/>
+      <x:c r="K149" s="8"/>
+      <x:c r="L149" s="8"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" s="8"/>
+      <x:c r="B150" s="8"/>
+      <x:c r="C150" s="8"/>
+      <x:c r="D150" s="8"/>
+      <x:c r="E150" s="8"/>
+      <x:c r="F150" s="8"/>
+      <x:c r="G150" s="8"/>
+      <x:c r="H150" s="8"/>
+      <x:c r="I150" s="8"/>
+      <x:c r="J150" s="8"/>
+      <x:c r="K150" s="8"/>
+      <x:c r="L150" s="8"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="8"/>
+      <x:c r="B151" s="8"/>
+      <x:c r="C151" s="8"/>
+      <x:c r="D151" s="8"/>
+      <x:c r="E151" s="8"/>
+      <x:c r="F151" s="8"/>
+      <x:c r="G151" s="8"/>
+      <x:c r="H151" s="8"/>
+      <x:c r="I151" s="8"/>
+      <x:c r="J151" s="8"/>
+      <x:c r="K151" s="8"/>
+      <x:c r="L151" s="8"/>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" s="8"/>
+      <x:c r="B152" s="8"/>
+      <x:c r="C152" s="8"/>
+      <x:c r="D152" s="8"/>
+      <x:c r="E152" s="8"/>
+      <x:c r="F152" s="8"/>
+      <x:c r="G152" s="8"/>
+      <x:c r="H152" s="8"/>
+      <x:c r="I152" s="8"/>
+      <x:c r="J152" s="8"/>
+      <x:c r="K152" s="8"/>
+      <x:c r="L152" s="8"/>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" s="8"/>
+      <x:c r="B153" s="8"/>
+      <x:c r="C153" s="8"/>
+      <x:c r="D153" s="8"/>
+      <x:c r="E153" s="8"/>
+      <x:c r="F153" s="8"/>
+      <x:c r="G153" s="8"/>
+      <x:c r="H153" s="8"/>
+      <x:c r="I153" s="8"/>
+      <x:c r="J153" s="8"/>
+      <x:c r="K153" s="8"/>
+      <x:c r="L153" s="8"/>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" s="8"/>
+      <x:c r="B154" s="8"/>
+      <x:c r="C154" s="8"/>
+      <x:c r="D154" s="8"/>
+      <x:c r="E154" s="8"/>
+      <x:c r="F154" s="8"/>
+      <x:c r="G154" s="8"/>
+      <x:c r="H154" s="8"/>
+      <x:c r="I154" s="8"/>
+      <x:c r="J154" s="8"/>
+      <x:c r="K154" s="8"/>
+      <x:c r="L154" s="8"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="8"/>
+      <x:c r="B155" s="8"/>
+      <x:c r="C155" s="8"/>
+      <x:c r="D155" s="8"/>
+      <x:c r="E155" s="8"/>
+      <x:c r="F155" s="8"/>
+      <x:c r="G155" s="8"/>
+      <x:c r="H155" s="8"/>
+      <x:c r="I155" s="8"/>
+      <x:c r="J155" s="8"/>
+      <x:c r="K155" s="8"/>
+      <x:c r="L155" s="8"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="8"/>
+      <x:c r="B156" s="8"/>
+      <x:c r="C156" s="8"/>
+      <x:c r="D156" s="8"/>
+      <x:c r="E156" s="8"/>
+      <x:c r="F156" s="8"/>
+      <x:c r="G156" s="8"/>
+      <x:c r="H156" s="8"/>
+      <x:c r="I156" s="8"/>
+      <x:c r="J156" s="8"/>
+      <x:c r="K156" s="8"/>
+      <x:c r="L156" s="8"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="8"/>
+      <x:c r="B157" s="8"/>
+      <x:c r="C157" s="8"/>
+      <x:c r="D157" s="8"/>
+      <x:c r="E157" s="8"/>
+      <x:c r="F157" s="8"/>
+      <x:c r="G157" s="8"/>
+      <x:c r="H157" s="8"/>
+      <x:c r="I157" s="8"/>
+      <x:c r="J157" s="8"/>
+      <x:c r="K157" s="8"/>
+      <x:c r="L157" s="8"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="8"/>
+      <x:c r="B158" s="8"/>
+      <x:c r="C158" s="8"/>
+      <x:c r="D158" s="8"/>
+      <x:c r="E158" s="8"/>
+      <x:c r="F158" s="8"/>
+      <x:c r="G158" s="8"/>
+      <x:c r="H158" s="8"/>
+      <x:c r="I158" s="8"/>
+      <x:c r="J158" s="8"/>
+      <x:c r="K158" s="8"/>
+      <x:c r="L158" s="8"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="8"/>
+      <x:c r="B159" s="8"/>
+      <x:c r="C159" s="8"/>
+      <x:c r="D159" s="8"/>
+      <x:c r="E159" s="8"/>
+      <x:c r="F159" s="8"/>
+      <x:c r="G159" s="8"/>
+      <x:c r="H159" s="8"/>
+      <x:c r="I159" s="8"/>
+      <x:c r="J159" s="8"/>
+      <x:c r="K159" s="8"/>
+      <x:c r="L159" s="8"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="8"/>
+      <x:c r="B160" s="8"/>
+      <x:c r="C160" s="8"/>
+      <x:c r="D160" s="8"/>
+      <x:c r="E160" s="8"/>
+      <x:c r="F160" s="8"/>
+      <x:c r="G160" s="8"/>
+      <x:c r="H160" s="8"/>
+      <x:c r="I160" s="8"/>
+      <x:c r="J160" s="8"/>
+      <x:c r="K160" s="8"/>
+      <x:c r="L160" s="8"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -715,9 +3068,9 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="40" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="44" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -729,6 +3082,314 @@
       </x:c>
       <x:c r="C1" s="4" t="str">
         <x:v>label</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>holder_type</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>staff</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>Study staff</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>holder_type</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>participant</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>Participant</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>holder_type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>contractor</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>Contractor / temporary staff</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>holder_type</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>visitor</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>Visitor / monitor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>holder_type</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>other</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>credential_role</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>principal_investigator</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Principal investigator</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>credential_role</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>sub_investigator</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Sub-investigator</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>credential_role</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>study_coordinator</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Study coordinator</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>credential_role</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>research_nurse</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>Research nurse</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>credential_role</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>clinician</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>Clinician</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>credential_role</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>laboratory_staff</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>Laboratory staff</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>credential_role</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>pharmacist</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>Pharmacist / pharmacy staff</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>credential_role</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>data_manager</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>Data manager</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>credential_role</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>monitor</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>Monitor / auditor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>credential_role</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>fieldworker</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>Fieldworker</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>credential_role</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>participant</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>Participant</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>credential_role</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>contractor</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>Contractor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>credential_role</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>other</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>provision_reason</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>initial_issue</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>Initial issue</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>provision_reason</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>replacement</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>Replacement card</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>provision_reason</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>renewal</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>Renewal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>provision_reason</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>role_change</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>Role or site change</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>provision_reason</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>reissue_after_loss</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>Reissue after loss</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>provision_reason</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>other</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>pin_length</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>4 digits</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>pin_length</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>6 digits</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>overwrite_policy</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>empty_only</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>Only write to an empty card</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>overwrite_policy</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>replace</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>Replace existing NDEF content</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -740,20 +3401,24 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="36" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="36" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="36" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="4" t="str">
         <x:v>form_title</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="4" t="str">
         <x:v>form_id</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="4" t="str">
         <x:v>version</x:v>
+      </x:c>
+      <x:c r="D1" s="4" t="str">
+        <x:v>default_language</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -761,10 +3426,13 @@
         <x:v>MethodMesh NFC — nfc_credential_provisioning</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>nfc_nfc_credential_provisioning</x:v>
+        <x:v>nfc_showcase_credential_provisioning</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>2026090701</x:v>
+        <x:v>2026092202</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>English</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
